--- a/data/B24_department_schedules_finals/İnşaat Mühendisliği.xlsx
+++ b/data/B24_department_schedules_finals/İnşaat Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/B24_department_schedules_finals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35943637-CD79-414F-AC78-A3A492FFBC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{35943637-CD79-414F-AC78-A3A492FFBC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C8E2E87-49C9-4BCC-A43A-948618638CA8}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="5940" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="82">
   <si>
     <t>Year:</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>C209,C213,CAD1</t>
+  </si>
+  <si>
+    <t>timeslots</t>
   </si>
 </sst>
 </file>
@@ -343,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -360,11 +363,18 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -443,18 +453,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F9B0E3CD-62B9-4A40-9983-B73A52C93363}" name="Table1" displayName="Table1" ref="A1:F34" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
-  <autoFilter ref="A1:F34" xr:uid="{F9B0E3CD-62B9-4A40-9983-B73A52C93363}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F9B0E3CD-62B9-4A40-9983-B73A52C93363}" name="Table1" displayName="Table1" ref="A1:G34" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
+  <autoFilter ref="A1:G34" xr:uid="{F9B0E3CD-62B9-4A40-9983-B73A52C93363}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F34">
     <sortCondition ref="B1:B34"/>
   </sortState>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{4217D035-DA80-4815-84AC-12E9DBABE214}" name="Year:" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{FB87D92A-DCBD-4F73-88EC-BA7CD9702E79}" name="Course ID" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{1AC2BE0A-2EEA-45B8-A74B-A82C5FB0B97A}" name="Date" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{DD3D160B-38E0-473E-ADCD-4E0E92D95048}" name="Rooms" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{EEB78D15-5F1B-4C70-A039-5F870979D854}" name="Course Name" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{A12AD2B5-0CF4-4181-ADA5-046FC0F6D1C2}" name="Rooms Used" dataDxfId="0"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{4217D035-DA80-4815-84AC-12E9DBABE214}" name="Year:" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{FB87D92A-DCBD-4F73-88EC-BA7CD9702E79}" name="Course ID" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{1AC2BE0A-2EEA-45B8-A74B-A82C5FB0B97A}" name="Date" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{DD3D160B-38E0-473E-ADCD-4E0E92D95048}" name="Rooms" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{EEB78D15-5F1B-4C70-A039-5F870979D854}" name="Course Name" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{A12AD2B5-0CF4-4181-ADA5-046FC0F6D1C2}" name="Rooms Used" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{D2748409-B01A-42B5-B54C-C4C4F98BD2EC}" name="timeslots" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -747,15 +758,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="31.6328125" customWidth="1"/>
-    <col min="6" max="6" width="33.1796875" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="31.59765625" customWidth="1"/>
+    <col min="6" max="6" width="33.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,8 +785,11 @@
       <c r="F1" s="1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -794,8 +808,12 @@
       <c r="F2" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G2" s="7">
+        <v>2</v>
+      </c>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -814,8 +832,12 @@
       <c r="F3" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G3" s="7">
+        <v>7</v>
+      </c>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -834,8 +856,12 @@
       <c r="F4" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G4" s="7">
+        <v>6</v>
+      </c>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -854,8 +880,12 @@
       <c r="F5" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G5" s="7">
+        <v>2</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -874,8 +904,11 @@
       <c r="F6" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G6" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -894,8 +927,12 @@
       <c r="F7" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G7" s="7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -914,8 +951,12 @@
       <c r="F8" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G8" s="7">
+        <v>2</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -934,8 +975,12 @@
       <c r="F9" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G9" s="7">
+        <v>6</v>
+      </c>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -954,8 +999,12 @@
       <c r="F10" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G10" s="7">
+        <v>1</v>
+      </c>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -974,8 +1023,11 @@
       <c r="F11" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -994,8 +1046,11 @@
       <c r="F12" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G12" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -1014,8 +1069,11 @@
       <c r="F13" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G13" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>3</v>
       </c>
@@ -1034,8 +1092,11 @@
       <c r="F14" s="4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -1054,8 +1115,11 @@
       <c r="F15" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G15" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>3</v>
       </c>
@@ -1074,8 +1138,11 @@
       <c r="F16" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G16" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>3</v>
       </c>
@@ -1094,8 +1161,11 @@
       <c r="F17" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G17" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -1114,8 +1184,11 @@
       <c r="F18" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1134,8 +1207,11 @@
       <c r="F19" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G19" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>3</v>
       </c>
@@ -1154,8 +1230,11 @@
       <c r="F20" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G20" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>3</v>
       </c>
@@ -1174,8 +1253,11 @@
       <c r="F21" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G21" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>3</v>
       </c>
@@ -1194,8 +1276,11 @@
       <c r="F22" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G22" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" s="5">
         <v>4</v>
       </c>
@@ -1214,8 +1299,11 @@
       <c r="F23" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G23" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -1234,8 +1322,11 @@
       <c r="F24" s="5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G24" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>4</v>
       </c>
@@ -1254,8 +1345,11 @@
       <c r="F25" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G25" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <v>4</v>
       </c>
@@ -1274,8 +1368,11 @@
       <c r="F26" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G26" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>4</v>
       </c>
@@ -1294,8 +1391,11 @@
       <c r="F27" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G27" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <v>4</v>
       </c>
@@ -1314,8 +1414,11 @@
       <c r="F28" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G28" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>4</v>
       </c>
@@ -1334,8 +1437,11 @@
       <c r="F29" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G29" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -1354,8 +1460,11 @@
       <c r="F30" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G30" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" s="5">
         <v>4</v>
       </c>
@@ -1374,8 +1483,11 @@
       <c r="F31" s="5" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G31" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" s="5">
         <v>4</v>
       </c>
@@ -1394,8 +1506,11 @@
       <c r="F32" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G32" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>1</v>
       </c>
@@ -1414,8 +1529,11 @@
       <c r="F33" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G33" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>1</v>
       </c>
@@ -1433,6 +1551,9 @@
       </c>
       <c r="F34" s="2" t="s">
         <v>72</v>
+      </c>
+      <c r="G34" s="7">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
